--- a/01_analyses_states/Rajasthan/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Rajasthan/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +415,13 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>24.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>47.4</v>
+        <v>46.7</v>
       </c>
       <c r="E4">
-        <v>54.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="5">
@@ -453,13 +453,13 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>31.6</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>12.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6">
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>21.1</v>
+        <v>13.3</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C7">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C8">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2">
-        <v>62.1</v>
+        <v>61.2</v>
       </c>
       <c r="D2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2">
-        <v>76.2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4">
-        <v>35.9</v>
+        <v>36.9</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>23.8</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/01_analyses_states/Rajasthan/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Rajasthan/results/SoIB_summaries.xlsx
@@ -402,7 +402,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3">
@@ -421,7 +421,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>23.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>44.4</v>
+        <v>46.7</v>
       </c>
       <c r="E4">
-        <v>65.40000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="5">
@@ -453,13 +453,13 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>3.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6">
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>22.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C7">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C8">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Rajasthan/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Rajasthan/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>6.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>22.6</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>46.7</v>
+        <v>32.3</v>
       </c>
       <c r="E4">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>12.9</v>
       </c>
       <c r="E5">
-        <v>6.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6">
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>13.3</v>
+        <v>3.2</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C8">
-        <v>298</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>392</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C2">
-        <v>61.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="D2">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E2">
-        <v>75</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="3">
@@ -782,10 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1.9</v>
+        <v>2.9</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -795,16 +801,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C4">
-        <v>36.9</v>
+        <v>27.2</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>19.1</v>
       </c>
     </row>
   </sheetData>
